--- a/resources/excel_templates/gb_t_32151_34_2024_appendix_b_v10.xlsx
+++ b/resources/excel_templates/gb_t_32151_34_2024_appendix_b_v10.xlsx
@@ -4937,7 +4937,7 @@
     <row r="6" ht="84" customHeight="1" s="42">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>数据提示：热力输入规则 V10（2.8.0）。H明确选已知焓并在F填写kJ/kg；不采用D/E辅助状态推算或替换已知值。自动物性暂不可用，不回退旧表。I选缺省值时G留空，由软件核验真实适用来源；选实测值须填G，空白不回缺省，0保留。购入热力在J确认热源位于本企业边界内/外，K声明供热燃料是否已计入本企业。内部且已计不重复计购热，不删除原燃料；其他内部/未知/冲突需澄清。输出不要求购入边界资格。L来源说明选填。新增数据行放本提示上方。</t>
+          <t>数据提示：热力输入规则 V10（2.8.0）。H明确选已知焓并在F填写kJ/kg；不采用D/E辅助状态推算或替换已知值。自动物性在D填MPa绝压，过热另填E的℃温度；仅干饱和或合法单相过热，不回退旧表。I选缺省值时G留空，由软件核验真实适用来源；选实测值须填G，空白不回缺省，0保留。购入热力在J确认热源位于本企业边界内/外，K声明供热燃料是否已计入本企业。内部且已计不重复计购热，不删除原燃料；其他内部/未知/冲突需澄清。输出不要求购入边界资格。L来源说明选填。新增数据行放本提示上方。</t>
         </is>
       </c>
     </row>
